--- a/Sep_2026/Daily Sale/11-09-26/Furqan.xlsx
+++ b/Sep_2026/Daily Sale/11-09-26/Furqan.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83432924-C24F-4114-9DF0-E243341CA29E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E67063EF-9F55-4FE2-8B6B-425F71955DD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="948" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47979,7 +47979,7 @@
       <c r="L4" s="395"/>
       <c r="M4" s="398">
         <f ca="1">TODAY()+1</f>
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="N4" s="398"/>
       <c r="O4" s="398"/>
@@ -48007,7 +48007,7 @@
       <c r="L5" s="395"/>
       <c r="M5" s="398">
         <f ca="1">M4-1</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="N5" s="394"/>
       <c r="O5" s="394"/>
@@ -54142,6 +54142,9 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:XEX51"/>
   <sheetFormatPr defaultColWidth="29.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -55641,7 +55644,7 @@
     <mergeCell ref="I5:I6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
